--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486998_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486998_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7858</v>
+        <v>5.1128</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9847</v>
+        <v>4.2525</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8011</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>2.336</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4846</v>
+        <v>0.8117</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2048</v>
+        <v>0.4726</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2798</v>
+        <v>0.3391</v>
       </c>
       <c r="V2" t="n">
         <v>0.9384</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3394</v>
+        <v>3.6335</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3648</v>
+        <v>4.1629</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0255</v>
+        <v>-0.5294</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1045</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3268</v>
+        <v>0.621</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6433</v>
+        <v>0.1548</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9701</v>
+        <v>0.4662</v>
       </c>
       <c r="V3" t="n">
         <v>2.7063</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8813</v>
+        <v>2.3353</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2485</v>
+        <v>4.7914</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3672</v>
+        <v>-2.4561</v>
       </c>
       <c r="G4" t="n">
         <v>3.22</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6962</v>
+        <v>0.1501</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8173</v>
+        <v>0.3602</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1211</v>
+        <v>-0.21</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8295</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2984</v>
+        <v>0.8033</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7312</v>
+        <v>-1.5869</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4327</v>
+        <v>2.3902</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0899</v>
+        <v>1.5026</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5344</v>
+        <v>1.7712</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4445</v>
+        <v>-0.2686</v>
       </c>
       <c r="J5" t="n">
-        <v>4.288</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6435</v>
+        <v>0.6263</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6445</v>
+        <v>-1.4081</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1981</v>
+        <v>2.2844</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1091</v>
+        <v>1.1449</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.089</v>
+        <v>1.1395</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.6694</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.3122</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8082</v>
+        <v>0.1221</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6856</v>
+        <v>0.0696</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1226</v>
+        <v>0.0524</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0698</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2035</v>
+        <v>0.3081</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0713</v>
+        <v>0.0333</v>
       </c>
       <c r="F6" t="n">
         <v>0.2748</v>
@@ -922,10 +922,10 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5502</v>
+        <v>-0.4456</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4611</v>
+        <v>-0.3565</v>
       </c>
       <c r="U6" t="n">
         <v>-0.0891</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0161</v>
+        <v>0.1734</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1099</v>
+        <v>-0.0146</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0938</v>
+        <v>0.188</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5026</v>
+        <v>0.1918</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7712</v>
+        <v>-0.2661</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2686</v>
+        <v>0.4579</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7818000000000001</v>
+        <v>0.0784</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6263</v>
+        <v>0.0389</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4081</v>
+        <v>0.0395</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2844</v>
+        <v>0.1134</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1449</v>
+        <v>-0.305</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1395</v>
+        <v>0.4184</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6974</v>
+        <v>-0.2237</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4534</v>
+        <v>-0.093</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.244</v>
+        <v>-0.1307</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0202</v>
+        <v>-0.1727</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1192</v>
+        <v>1.3786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09909999999999999</v>
+        <v>-1.5513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1918</v>
+        <v>1.0899</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2661</v>
+        <v>1.5344</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4579</v>
+        <v>-0.4445</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0784</v>
+        <v>4.288</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0389</v>
+        <v>3.6435</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>0.6445</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1134</v>
+        <v>-3.1981</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.305</v>
+        <v>-2.1091</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4184</v>
+        <v>-1.089</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.3122</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4173</v>
+        <v>0.3371</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1976</v>
+        <v>0.333</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2197</v>
+        <v>0.0041</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5921</v>
+        <v>-0.3706</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8398</v>
+        <v>-2.9444</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2477</v>
+        <v>2.5738</v>
       </c>
       <c r="G9" t="n">
         <v>2.5819</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0384</v>
+        <v>0.1831</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2517</v>
+        <v>0.1471</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2901</v>
+        <v>0.036</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2875</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7239</v>
+        <v>-0.3804</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4854</v>
+        <v>2.7992</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2093</v>
+        <v>-3.1796</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2985</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.22</v>
+        <v>-0.8766</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5192</v>
+        <v>-0.2054</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7008</v>
+        <v>-0.6711</v>
       </c>
       <c r="V10" t="n">
         <v>1.7679</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8013</v>
+        <v>-2.1695</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8318</v>
+        <v>0.3747</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6331</v>
+        <v>-2.5442</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1391</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.346</v>
+        <v>-0.0223</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6778</v>
+        <v>0.2207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3319</v>
+        <v>-0.243</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8295</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6613</v>
+        <v>-3.2503</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4603</v>
+        <v>-2.8714</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.201</v>
+        <v>-0.3789</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3604</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1572</v>
+        <v>0.2538</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5697</v>
+        <v>0.0192</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4125</v>
+        <v>0.2346</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5277</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6935</v>
+        <v>6.022899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0459</v>
+        <v>10.3753</v>
       </c>
       <c r="F13" t="n">
         <v>-4.352300000000001</v>
@@ -1444,7 +1444,7 @@
         <v>11.8179</v>
       </c>
       <c r="K13" t="n">
-        <v>8.584100000000001</v>
+        <v>8.584099999999999</v>
       </c>
       <c r="L13" t="n">
         <v>3.2339</v>
@@ -1456,7 +1456,7 @@
         <v>-6.9132</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2526999999999999</v>
+        <v>0.2527000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-2.0534</v>
@@ -1468,13 +1468,13 @@
         <v>12.3204</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5812999999999998</v>
+        <v>0.9107000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7929</v>
+        <v>1.1223</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2116999999999999</v>
+        <v>-0.2114999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.0082</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7123</v>
+        <v>4.442</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3747</v>
+        <v>3.2701</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3376</v>
+        <v>1.1719</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4194</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0442</v>
+        <v>0.7739</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4144</v>
+        <v>0.3097</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6298</v>
+        <v>0.4641</v>
       </c>
       <c r="V14" t="n">
         <v>2.2394</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6309</v>
+        <v>2.4715</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9113</v>
+        <v>3.7606</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2804</v>
+        <v>-1.2891</v>
       </c>
       <c r="G15" t="n">
         <v>2.9565</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5594</v>
+        <v>0.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7704</v>
+        <v>0.6198</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.211</v>
+        <v>-0.2198</v>
       </c>
       <c r="V15" t="n">
         <v>-2.117</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8854</v>
+        <v>2.3178</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0396</v>
+        <v>3.3534</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1542</v>
+        <v>-1.0356</v>
       </c>
       <c r="G16" t="n">
         <v>1.4538</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1844</v>
+        <v>0.2479</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.124</v>
+        <v>0.1898</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0604</v>
+        <v>0.0581</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0594</v>
+        <v>2.278</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7038</v>
+        <v>1.436</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3556</v>
+        <v>0.8421</v>
       </c>
       <c r="G17" t="n">
         <v>1.3353</v>
@@ -1780,13 +1780,13 @@
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5626</v>
+        <v>-0.3439</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1702</v>
+        <v>-0.438</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3923</v>
+        <v>0.0941</v>
       </c>
       <c r="V17" t="n">
         <v>2.108</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5285</v>
+        <v>0.5399</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0998</v>
+        <v>0.7937</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6282</v>
+        <v>-0.2538</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5466</v>
+        <v>-1.2963</v>
       </c>
       <c r="H18" t="n">
-        <v>0.227</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7736</v>
+        <v>-0.4238</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5995</v>
+        <v>0.4211</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0584</v>
+        <v>-0.0126</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6579</v>
+        <v>0.4338</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0528</v>
+        <v>-1.7174</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1686</v>
+        <v>-0.8599</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1157</v>
+        <v>-0.8575</v>
       </c>
       <c r="P18" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4591</v>
+        <v>0.6576</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4997</v>
+        <v>0.2207</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0407</v>
+        <v>0.4369</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3911</v>
+        <v>0.2583</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7598</v>
+        <v>-0.5182</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1509</v>
+        <v>0.7764</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3743</v>
+        <v>-0.5466</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2847</v>
+        <v>0.227</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9104</v>
+        <v>-0.7736</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8452</v>
+        <v>-0.5995</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9378</v>
+        <v>0.0584</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9074</v>
+        <v>-0.6579</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.2195</v>
+        <v>0.0528</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2225</v>
+        <v>0.1686</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.997</v>
+        <v>-0.1157</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5281</v>
+        <v>0.1889</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0854</v>
+        <v>0.0813</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6135</v>
+        <v>0.1075</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.777</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.48</v>
+        <v>-0.8602</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0615</v>
+        <v>2.6552</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5415</v>
+        <v>-3.5154</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2963</v>
+        <v>-0.3743</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-1.2847</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4238</v>
+        <v>0.9104</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4211</v>
+        <v>2.8452</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0126</v>
+        <v>0.9378</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4338</v>
+        <v>1.9074</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7174</v>
+        <v>-3.2195</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8599</v>
+        <v>-2.2225</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8575</v>
+        <v>-0.997</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3623</v>
+        <v>0.0591</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5115</v>
+        <v>-0.19</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1492</v>
+        <v>0.249</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>-1.777</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.777</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.966</v>
+        <v>-2.375</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0249</v>
+        <v>-2.9203</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0589</v>
+        <v>0.5453</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9768</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5785</v>
+        <v>0.0125</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4147</v>
+        <v>-0.3101</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1638</v>
+        <v>0.3226</v>
       </c>
       <c r="V21" t="n">
         <v>1.1786</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9993</v>
+        <v>-2.6195</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3353</v>
+        <v>-2.7612</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.664</v>
+        <v>0.1417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5099</v>
+        <v>-3.2717</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1102</v>
+        <v>-1.2747</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3997</v>
+        <v>-1.997</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1247</v>
+        <v>-2.5329</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1908</v>
+        <v>-1.1382</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9338</v>
+        <v>-1.3947</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6147</v>
+        <v>-0.7388</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0807</v>
+        <v>-0.1365</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4659</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.6694</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6049</v>
+        <v>0.0281</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4066</v>
+        <v>-0.0311</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0115</v>
+        <v>0.0592</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.2349</v>
+        <v>0.8295</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2402</v>
+        <v>0.8295</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4755</v>
+        <v>-3.0812</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3888</v>
+        <v>-0.9629</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0867</v>
+        <v>-2.1183</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2717</v>
+        <v>2.5099</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2747</v>
+        <v>0.1102</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.997</v>
+        <v>2.3997</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5329</v>
+        <v>3.1247</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1382</v>
+        <v>1.1908</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3947</v>
+        <v>1.9338</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7388</v>
+        <v>-0.6147</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1365</v>
+        <v>-1.0807</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.4659</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.828</v>
+        <v>-0.6868</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6587</v>
+        <v>-0.221</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1692</v>
+        <v>-0.4658</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8295</v>
+        <v>-2.2349</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8295</v>
+        <v>0.2402</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.4751</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1981</v>
+        <v>-6.9732</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6495</v>
+        <v>-3.7541</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5486</v>
+        <v>-3.2191</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5277</v>
@@ -2326,13 +2326,13 @@
         <v>1.8481</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0516</v>
+        <v>0.1733</v>
       </c>
       <c r="T24" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.0196</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1365</v>
+        <v>0.1929</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4135</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.6935</v>
+        <v>-3.6016</v>
       </c>
       <c r="E25" t="n">
-        <v>4.352399999999999</v>
+        <v>4.352299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.046</v>
+        <v>-7.9539</v>
       </c>
       <c r="G25" t="n">
         <v>-5.157299999999999</v>
@@ -2377,7 +2377,7 @@
         <v>-3.4866</v>
       </c>
       <c r="J25" t="n">
-        <v>6.660799999999998</v>
+        <v>6.6608</v>
       </c>
       <c r="K25" t="n">
         <v>6.913500000000001</v>
@@ -2389,13 +2389,13 @@
         <v>-11.8181</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.584200000000001</v>
+        <v>-8.584199999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-3.2339</v>
       </c>
       <c r="P25" t="n">
-        <v>2.0536</v>
+        <v>2.053599999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.3204</v>
@@ -2404,13 +2404,13 @@
         <v>14.3741</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5814999999999997</v>
+        <v>1.5106</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2116000000000002</v>
+        <v>0.2115</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7928999999999999</v>
+        <v>1.2988</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0083</v>
